--- a/docs/handoff/v159/datasetTypologyV159.xlsx
+++ b/docs/handoff/v159/datasetTypologyV159.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U0</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U0</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U0</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
